--- a/backend/data/financials_by_company/1166.HK.xlsx
+++ b/backend/data/financials_by_company/1166.HK.xlsx
@@ -667,55 +667,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>417917.228451</v>
+        <v>12676191.325922</v>
       </c>
       <c r="C2" t="n">
-        <v>0.195654</v>
+        <v>0.110157</v>
       </c>
       <c r="D2" t="n">
-        <v>-88532000</v>
+        <v>100835000</v>
       </c>
       <c r="E2" t="n">
-        <v>2136000</v>
+        <v>115074000</v>
       </c>
       <c r="F2" t="n">
-        <v>2136000</v>
+        <v>115074000</v>
       </c>
       <c r="G2" t="n">
-        <v>-88516000</v>
+        <v>156346000</v>
       </c>
       <c r="H2" t="n">
-        <v>5052000</v>
+        <v>11403000</v>
       </c>
       <c r="I2" t="n">
-        <v>728476000</v>
+        <v>374815000</v>
       </c>
       <c r="J2" t="n">
-        <v>-86396000</v>
+        <v>215909000</v>
       </c>
       <c r="K2" t="n">
-        <v>-91448000</v>
+        <v>204506000</v>
       </c>
       <c r="L2" t="n">
-        <v>-8744000</v>
+        <v>-2467000</v>
       </c>
       <c r="M2" t="n">
-        <v>19508000</v>
+        <v>15875000</v>
       </c>
       <c r="N2" t="n">
-        <v>10909000</v>
+        <v>13408000</v>
       </c>
       <c r="O2" t="n">
-        <v>-90234082.771549</v>
+        <v>53948191.325922</v>
       </c>
       <c r="P2" t="n">
-        <v>-88516000</v>
+        <v>156346000</v>
       </c>
       <c r="Q2" t="n">
-        <v>822814000</v>
+        <v>454193000</v>
       </c>
       <c r="R2" t="n">
         <v>118726617</v>
@@ -724,145 +724,143 @@
         <v>118726617</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.75</v>
+        <v>1.32</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.75</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>-88516000</v>
+        <v>156346000</v>
       </c>
       <c r="W2" t="n">
-        <v>-88516000</v>
+        <v>156346000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-88516000</v>
+        <v>156346000</v>
       </c>
       <c r="Z2" t="n">
-        <v>731000</v>
+        <v>-11506000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-89247000</v>
+        <v>167852000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-89247000</v>
+        <v>167852000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-21709000</v>
+        <v>20779000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-110956000</v>
+        <v>188631000</v>
       </c>
       <c r="AE2" t="n">
-        <v>7884000</v>
+        <v>1176000</v>
       </c>
       <c r="AF2" t="n">
-        <v>4065000</v>
+        <v>112307000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-2978000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>4653000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>13115000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>-1087000</v>
+        <v>-130075000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-8744000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>145000</v>
-      </c>
+        <v>-2467000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>19508000</v>
+        <v>15875000</v>
       </c>
       <c r="AM2" t="n">
-        <v>10909000</v>
+        <v>13408000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-27114000</v>
+        <v>-21144000</v>
       </c>
       <c r="AO2" t="n">
-        <v>94338000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2317000</v>
-      </c>
+        <v>79378000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>92021000</v>
+        <v>79980000</v>
       </c>
       <c r="AR2" t="n">
-        <v>7912000</v>
+        <v>10430000</v>
       </c>
       <c r="AS2" t="n">
-        <v>84109000</v>
+        <v>69550000</v>
       </c>
       <c r="AT2" t="n">
-        <v>67224000</v>
+        <v>58234000</v>
       </c>
       <c r="AU2" t="n">
-        <v>728476000</v>
+        <v>374815000</v>
       </c>
       <c r="AV2" t="n">
-        <v>795700000</v>
+        <v>433049000</v>
       </c>
       <c r="AW2" t="n">
-        <v>795700000</v>
+        <v>433049000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-21760000</v>
+        <v>-8007393.531548</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.101617</v>
       </c>
       <c r="D3" t="n">
-        <v>-51292000</v>
+        <v>-5468000</v>
       </c>
       <c r="E3" t="n">
-        <v>-87040000</v>
+        <v>-78800000</v>
       </c>
       <c r="F3" t="n">
-        <v>-87040000</v>
+        <v>-78800000</v>
       </c>
       <c r="G3" t="n">
-        <v>-176246000</v>
+        <v>-102218000</v>
       </c>
       <c r="H3" t="n">
-        <v>6098000</v>
+        <v>7101000</v>
       </c>
       <c r="I3" t="n">
-        <v>362161000</v>
+        <v>404843000</v>
       </c>
       <c r="J3" t="n">
-        <v>-138332000</v>
+        <v>-84268000</v>
       </c>
       <c r="K3" t="n">
-        <v>-144430000</v>
+        <v>-91369000</v>
       </c>
       <c r="L3" t="n">
-        <v>-5783000</v>
+        <v>-7032000</v>
       </c>
       <c r="M3" t="n">
-        <v>19768000</v>
+        <v>21270000</v>
       </c>
       <c r="N3" t="n">
-        <v>13985000</v>
+        <v>14238000</v>
       </c>
       <c r="O3" t="n">
-        <v>-110966000</v>
+        <v>-31425393.531548</v>
       </c>
       <c r="P3" t="n">
-        <v>-176246000</v>
+        <v>-102218000</v>
       </c>
       <c r="Q3" t="n">
-        <v>435744000</v>
+        <v>482591000</v>
       </c>
       <c r="R3" t="n">
         <v>118726617</v>
@@ -871,145 +869,145 @@
         <v>118726617</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.48</v>
+        <v>-0.86</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.48</v>
+        <v>-0.86</v>
       </c>
       <c r="V3" t="n">
-        <v>-176246000</v>
+        <v>-102218000</v>
       </c>
       <c r="W3" t="n">
-        <v>-176246000</v>
+        <v>-102218000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-176246000</v>
+        <v>-102218000</v>
       </c>
       <c r="Z3" t="n">
-        <v>513000</v>
+        <v>-1025000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-176759000</v>
+        <v>-101193000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-176759000</v>
+        <v>-101193000</v>
       </c>
       <c r="AC3" t="n">
-        <v>12561000</v>
+        <v>-11446000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-164198000</v>
+        <v>-112639000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1244000</v>
+        <v>935000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-86569000</v>
+        <v>-72987000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5475000</v>
+        <v>2218000</v>
       </c>
       <c r="AH3" t="n">
-        <v>4609000</v>
+        <v>-2614000</v>
       </c>
       <c r="AI3" t="n">
-        <v>92044000</v>
+        <v>70769000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-5783000</v>
+        <v>-7032000</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>19768000</v>
+        <v>21270000</v>
       </c>
       <c r="AM3" t="n">
-        <v>13985000</v>
+        <v>14238000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-61428000</v>
+        <v>-11070000</v>
       </c>
       <c r="AO3" t="n">
-        <v>73583000</v>
+        <v>77748000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4609000</v>
+        <v>-2614000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>69278000</v>
+        <v>80514000</v>
       </c>
       <c r="AR3" t="n">
-        <v>7650000</v>
+        <v>7413000</v>
       </c>
       <c r="AS3" t="n">
-        <v>61628000</v>
+        <v>73101000</v>
       </c>
       <c r="AT3" t="n">
-        <v>12155000</v>
+        <v>66678000</v>
       </c>
       <c r="AU3" t="n">
-        <v>362161000</v>
+        <v>404843000</v>
       </c>
       <c r="AV3" t="n">
-        <v>374316000</v>
+        <v>471521000</v>
       </c>
       <c r="AW3" t="n">
-        <v>374316000</v>
+        <v>471521000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-8007393.531548</v>
+        <v>-21760000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.101617</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-5468000</v>
+        <v>-51292000</v>
       </c>
       <c r="E4" t="n">
-        <v>-78800000</v>
+        <v>-87040000</v>
       </c>
       <c r="F4" t="n">
-        <v>-78800000</v>
+        <v>-87040000</v>
       </c>
       <c r="G4" t="n">
-        <v>-102218000</v>
+        <v>-176246000</v>
       </c>
       <c r="H4" t="n">
-        <v>7101000</v>
+        <v>6098000</v>
       </c>
       <c r="I4" t="n">
-        <v>404843000</v>
+        <v>362161000</v>
       </c>
       <c r="J4" t="n">
-        <v>-84268000</v>
+        <v>-138332000</v>
       </c>
       <c r="K4" t="n">
-        <v>-91369000</v>
+        <v>-144430000</v>
       </c>
       <c r="L4" t="n">
-        <v>-7032000</v>
+        <v>-5783000</v>
       </c>
       <c r="M4" t="n">
-        <v>21270000</v>
+        <v>19768000</v>
       </c>
       <c r="N4" t="n">
-        <v>14238000</v>
+        <v>13985000</v>
       </c>
       <c r="O4" t="n">
-        <v>-31425393.531548</v>
+        <v>-110966000</v>
       </c>
       <c r="P4" t="n">
-        <v>-102218000</v>
+        <v>-176246000</v>
       </c>
       <c r="Q4" t="n">
-        <v>482591000</v>
+        <v>435744000</v>
       </c>
       <c r="R4" t="n">
         <v>118726617</v>
@@ -1018,145 +1016,145 @@
         <v>118726617</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.86</v>
+        <v>-1.48</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.86</v>
+        <v>-1.48</v>
       </c>
       <c r="V4" t="n">
-        <v>-102218000</v>
+        <v>-176246000</v>
       </c>
       <c r="W4" t="n">
-        <v>-102218000</v>
+        <v>-176246000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-102218000</v>
+        <v>-176246000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1025000</v>
+        <v>513000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-101193000</v>
+        <v>-176759000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-101193000</v>
+        <v>-176759000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-11446000</v>
+        <v>12561000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-112639000</v>
+        <v>-164198000</v>
       </c>
       <c r="AE4" t="n">
-        <v>935000</v>
+        <v>1244000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-72987000</v>
+        <v>-86569000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2218000</v>
+        <v>-5475000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-2614000</v>
+        <v>4609000</v>
       </c>
       <c r="AI4" t="n">
-        <v>70769000</v>
+        <v>92044000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-7032000</v>
+        <v>-5783000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>21270000</v>
+        <v>19768000</v>
       </c>
       <c r="AM4" t="n">
-        <v>14238000</v>
+        <v>13985000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-11070000</v>
+        <v>-61428000</v>
       </c>
       <c r="AO4" t="n">
-        <v>77748000</v>
+        <v>73583000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2614000</v>
+        <v>4609000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>80514000</v>
+        <v>69278000</v>
       </c>
       <c r="AR4" t="n">
-        <v>7413000</v>
+        <v>7650000</v>
       </c>
       <c r="AS4" t="n">
-        <v>73101000</v>
+        <v>61628000</v>
       </c>
       <c r="AT4" t="n">
-        <v>66678000</v>
+        <v>12155000</v>
       </c>
       <c r="AU4" t="n">
-        <v>404843000</v>
+        <v>362161000</v>
       </c>
       <c r="AV4" t="n">
-        <v>471521000</v>
+        <v>374316000</v>
       </c>
       <c r="AW4" t="n">
-        <v>471521000</v>
+        <v>374316000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>12676191.325922</v>
+        <v>417917.228451</v>
       </c>
       <c r="C5" t="n">
-        <v>0.110157</v>
+        <v>0.195654</v>
       </c>
       <c r="D5" t="n">
-        <v>100835000</v>
+        <v>-88532000</v>
       </c>
       <c r="E5" t="n">
-        <v>115074000</v>
+        <v>2136000</v>
       </c>
       <c r="F5" t="n">
-        <v>115074000</v>
+        <v>2136000</v>
       </c>
       <c r="G5" t="n">
-        <v>156346000</v>
+        <v>-88516000</v>
       </c>
       <c r="H5" t="n">
-        <v>11403000</v>
+        <v>5052000</v>
       </c>
       <c r="I5" t="n">
-        <v>374815000</v>
+        <v>728476000</v>
       </c>
       <c r="J5" t="n">
-        <v>215909000</v>
+        <v>-86396000</v>
       </c>
       <c r="K5" t="n">
-        <v>204506000</v>
+        <v>-91448000</v>
       </c>
       <c r="L5" t="n">
-        <v>-2467000</v>
+        <v>-8744000</v>
       </c>
       <c r="M5" t="n">
-        <v>15875000</v>
+        <v>19508000</v>
       </c>
       <c r="N5" t="n">
-        <v>13408000</v>
+        <v>10909000</v>
       </c>
       <c r="O5" t="n">
-        <v>53948191.325922</v>
+        <v>-90234082.771549</v>
       </c>
       <c r="P5" t="n">
-        <v>156346000</v>
+        <v>-88516000</v>
       </c>
       <c r="Q5" t="n">
-        <v>454193000</v>
+        <v>822814000</v>
       </c>
       <c r="R5" t="n">
         <v>118726617</v>
@@ -1165,90 +1163,92 @@
         <v>118726617</v>
       </c>
       <c r="T5" t="n">
-        <v>1.32</v>
+        <v>-0.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.32</v>
+        <v>-0.75</v>
       </c>
       <c r="V5" t="n">
-        <v>156346000</v>
+        <v>-88516000</v>
       </c>
       <c r="W5" t="n">
-        <v>156346000</v>
+        <v>-88516000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>156346000</v>
+        <v>-88516000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-11506000</v>
+        <v>731000</v>
       </c>
       <c r="AA5" t="n">
-        <v>167852000</v>
+        <v>-89247000</v>
       </c>
       <c r="AB5" t="n">
-        <v>167852000</v>
+        <v>-89247000</v>
       </c>
       <c r="AC5" t="n">
-        <v>20779000</v>
+        <v>-21709000</v>
       </c>
       <c r="AD5" t="n">
-        <v>188631000</v>
+        <v>-110956000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1176000</v>
+        <v>7884000</v>
       </c>
       <c r="AF5" t="n">
-        <v>112307000</v>
+        <v>4065000</v>
       </c>
       <c r="AG5" t="n">
-        <v>4653000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>13115000</v>
-      </c>
+        <v>-2978000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-130075000</v>
+        <v>-1087000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-2467000</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>-8744000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>145000</v>
+      </c>
       <c r="AL5" t="n">
-        <v>15875000</v>
+        <v>19508000</v>
       </c>
       <c r="AM5" t="n">
-        <v>13408000</v>
+        <v>10909000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-21144000</v>
+        <v>-27114000</v>
       </c>
       <c r="AO5" t="n">
-        <v>79378000</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>94338000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2317000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>79980000</v>
+        <v>92021000</v>
       </c>
       <c r="AR5" t="n">
-        <v>10430000</v>
+        <v>7912000</v>
       </c>
       <c r="AS5" t="n">
-        <v>69550000</v>
+        <v>84109000</v>
       </c>
       <c r="AT5" t="n">
-        <v>58234000</v>
+        <v>67224000</v>
       </c>
       <c r="AU5" t="n">
-        <v>374815000</v>
+        <v>728476000</v>
       </c>
       <c r="AV5" t="n">
-        <v>433049000</v>
+        <v>795700000</v>
       </c>
       <c r="AW5" t="n">
-        <v>433049000</v>
+        <v>795700000</v>
       </c>
     </row>
   </sheetData>
@@ -1614,58 +1614,58 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>118726617</v>
+        <v>118726600</v>
       </c>
       <c r="C2" t="n">
-        <v>118726617</v>
+        <v>118726600</v>
       </c>
       <c r="D2" t="n">
-        <v>159908000</v>
+        <v>202686000</v>
       </c>
       <c r="E2" t="n">
-        <v>264231000</v>
+        <v>272841000</v>
       </c>
       <c r="F2" t="n">
-        <v>800489000</v>
+        <v>1200263000</v>
       </c>
       <c r="G2" t="n">
-        <v>1062923000</v>
+        <v>1469902000</v>
       </c>
       <c r="H2" t="n">
-        <v>-46135000</v>
+        <v>68327000</v>
       </c>
       <c r="I2" t="n">
-        <v>800489000</v>
+        <v>1200263000</v>
       </c>
       <c r="J2" t="n">
-        <v>1797000</v>
+        <v>3202000</v>
       </c>
       <c r="K2" t="n">
-        <v>800489000</v>
+        <v>1200263000</v>
       </c>
       <c r="L2" t="n">
-        <v>906319000</v>
+        <v>1220706000</v>
       </c>
       <c r="M2" t="n">
-        <v>798726000</v>
+        <v>1198550000</v>
       </c>
       <c r="N2" t="n">
-        <v>-1763000</v>
+        <v>-1713000</v>
       </c>
       <c r="O2" t="n">
-        <v>800489000</v>
+        <v>1200263000</v>
       </c>
       <c r="P2" t="n">
-        <v>233000</v>
+        <v>1518000</v>
       </c>
       <c r="Q2" t="n">
-        <v>99901000</v>
+        <v>108253000</v>
       </c>
       <c r="R2" t="n">
-        <v>-1745636000</v>
+        <v>-1388526000</v>
       </c>
       <c r="S2" t="n">
         <v>2440792000</v>
@@ -1677,138 +1677,156 @@
         <v>23745000</v>
       </c>
       <c r="V2" t="n">
-        <v>568589000</v>
+        <v>565752000</v>
       </c>
       <c r="W2" t="n">
-        <v>163767000</v>
+        <v>159942000</v>
       </c>
       <c r="X2" t="n">
-        <v>4288000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>22723000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>27270000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>52962000</v>
+        <v>88190000</v>
       </c>
       <c r="AA2" t="n">
-        <v>106517000</v>
+        <v>21759000</v>
       </c>
       <c r="AB2" t="n">
-        <v>687000</v>
+        <v>1316000</v>
       </c>
       <c r="AC2" t="n">
-        <v>105830000</v>
+        <v>20443000</v>
       </c>
       <c r="AD2" t="n">
-        <v>404822000</v>
+        <v>405810000</v>
       </c>
       <c r="AE2" t="n">
-        <v>157714000</v>
+        <v>251082000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1110000</v>
+        <v>1886000</v>
       </c>
       <c r="AG2" t="n">
-        <v>156604000</v>
+        <v>249196000</v>
       </c>
       <c r="AH2" t="n">
-        <v>231933000</v>
+        <v>148902000</v>
       </c>
       <c r="AI2" t="n">
-        <v>113184000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>64200000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
       <c r="AK2" t="n">
-        <v>117763000</v>
+        <v>84702000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1367315000</v>
+        <v>1764302000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1008628000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+        <v>1290165000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1632000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
       <c r="AP2" t="n">
-        <v>3851000</v>
+        <v>35867000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3106000</v>
+        <v>24267000</v>
       </c>
       <c r="AR2" t="n">
-        <v>745000</v>
+        <v>11600000</v>
       </c>
       <c r="AS2" t="n">
-        <v>586369000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>650996000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>557560000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>557560000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>418408000</v>
+        <v>593605000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-986804000</v>
+        <v>-907807000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1405212000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+        <v>1501412000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1632000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>24933000</v>
+      </c>
       <c r="BA2" t="n">
-        <v>179029000</v>
+        <v>263507000</v>
       </c>
       <c r="BB2" t="n">
-        <v>53581000</v>
+        <v>62278000</v>
       </c>
       <c r="BC2" t="n">
-        <v>4898000</v>
+        <v>6306000</v>
       </c>
       <c r="BD2" t="n">
-        <v>1167704000</v>
+        <v>1167689000</v>
       </c>
       <c r="BE2" t="n">
-        <v>358687000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>474137000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>72150000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>7567000</v>
+        <v>3446000</v>
       </c>
       <c r="BH2" t="n">
-        <v>25342000</v>
+        <v>46593000</v>
       </c>
       <c r="BI2" t="n">
-        <v>9939000</v>
+        <v>28835000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>6354000</v>
+        <v>1275000</v>
       </c>
       <c r="BK2" t="n">
-        <v>9049000</v>
+        <v>16483000</v>
       </c>
       <c r="BL2" t="n">
-        <v>125674000</v>
+        <v>187427000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9665000</v>
+        <v>7865000</v>
       </c>
       <c r="BN2" t="n">
-        <v>84113000</v>
+        <v>84612000</v>
       </c>
       <c r="BO2" t="n">
-        <v>106326000</v>
+        <v>72044000</v>
       </c>
       <c r="BP2" t="n">
-        <v>3800000</v>
+        <v>5091000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>102526000</v>
+        <v>66953000</v>
       </c>
       <c r="BR2" t="n">
-        <v>102526000</v>
+        <v>66953000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>118726600</v>
@@ -1817,47 +1835,47 @@
         <v>118726600</v>
       </c>
       <c r="D3" t="n">
-        <v>175276000</v>
+        <v>422655000</v>
       </c>
       <c r="E3" t="n">
-        <v>264001000</v>
+        <v>495992000</v>
       </c>
       <c r="F3" t="n">
-        <v>889204000</v>
+        <v>1089342000</v>
       </c>
       <c r="G3" t="n">
-        <v>1150145000</v>
+        <v>1583343000</v>
       </c>
       <c r="H3" t="n">
-        <v>9163000</v>
+        <v>64397000</v>
       </c>
       <c r="I3" t="n">
-        <v>889204000</v>
+        <v>1089342000</v>
       </c>
       <c r="J3" t="n">
-        <v>3060000</v>
+        <v>1991000</v>
       </c>
       <c r="K3" t="n">
-        <v>889204000</v>
+        <v>1089342000</v>
       </c>
       <c r="L3" t="n">
-        <v>1020968000</v>
+        <v>1403306000</v>
       </c>
       <c r="M3" t="n">
-        <v>888155000</v>
+        <v>1088680000</v>
       </c>
       <c r="N3" t="n">
-        <v>-1049000</v>
+        <v>-662000</v>
       </c>
       <c r="O3" t="n">
-        <v>889204000</v>
+        <v>1089342000</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>99901000</v>
+        <v>108253000</v>
       </c>
       <c r="R3" t="n">
-        <v>-1657120000</v>
+        <v>-1489226000</v>
       </c>
       <c r="S3" t="n">
         <v>2440792000</v>
@@ -1869,148 +1887,154 @@
         <v>23745000</v>
       </c>
       <c r="V3" t="n">
-        <v>558705000</v>
+        <v>603784000</v>
       </c>
       <c r="W3" t="n">
-        <v>215780000</v>
+        <v>306610000</v>
       </c>
       <c r="X3" t="n">
-        <v>7334000</v>
+        <v>27491000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>34768000</v>
       </c>
       <c r="Z3" t="n">
-        <v>74884000</v>
+        <v>87138000</v>
       </c>
       <c r="AA3" t="n">
-        <v>133562000</v>
+        <v>314195000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1798000</v>
+        <v>231000</v>
       </c>
       <c r="AC3" t="n">
-        <v>131764000</v>
+        <v>313964000</v>
       </c>
       <c r="AD3" t="n">
-        <v>342925000</v>
+        <v>297174000</v>
       </c>
       <c r="AE3" t="n">
-        <v>130439000</v>
+        <v>181797000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1262000</v>
+        <v>1760000</v>
       </c>
       <c r="AG3" t="n">
-        <v>129177000</v>
+        <v>180037000</v>
       </c>
       <c r="AH3" t="n">
-        <v>195486000</v>
+        <v>107222000</v>
       </c>
       <c r="AI3" t="n">
-        <v>140313000</v>
+        <v>52491000</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>55173000</v>
+        <v>54731000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1446860000</v>
+        <v>1692464000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1094772000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>1330893000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
       <c r="AO3" t="n">
+        <v>12877000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>12717000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9040000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3677000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>767219000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>486820000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>486820000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>516185000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-931483000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1447668000</v>
+      </c>
+      <c r="AY3" t="n">
         <v>0</v>
       </c>
-      <c r="AP3" t="n">
-        <v>4713000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1956000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2757000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>669164000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>394772000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>394772000</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>420895000</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-985221000</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1406116000</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>17709000</v>
+        <v>21458000</v>
       </c>
       <c r="BA3" t="n">
-        <v>178204000</v>
+        <v>215107000</v>
       </c>
       <c r="BB3" t="n">
-        <v>55030000</v>
+        <v>58933000</v>
       </c>
       <c r="BC3" t="n">
-        <v>5168000</v>
+        <v>5910000</v>
       </c>
       <c r="BD3" t="n">
-        <v>1167714000</v>
+        <v>1167718000</v>
       </c>
       <c r="BE3" t="n">
-        <v>352088000</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>361571000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
       <c r="BG3" t="n">
-        <v>6932000</v>
+        <v>5651000</v>
       </c>
       <c r="BH3" t="n">
-        <v>23818000</v>
+        <v>33442000</v>
       </c>
       <c r="BI3" t="n">
-        <v>9709000</v>
+        <v>20646000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>6306000</v>
+        <v>111000</v>
       </c>
       <c r="BK3" t="n">
-        <v>7803000</v>
+        <v>12685000</v>
       </c>
       <c r="BL3" t="n">
-        <v>162488000</v>
+        <v>160050000</v>
       </c>
       <c r="BM3" t="n">
-        <v>9613000</v>
+        <v>10267000</v>
       </c>
       <c r="BN3" t="n">
-        <v>57642000</v>
+        <v>74017000</v>
       </c>
       <c r="BO3" t="n">
-        <v>91595000</v>
+        <v>78144000</v>
       </c>
       <c r="BP3" t="n">
-        <v>5930000</v>
+        <v>6798000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>85665000</v>
+        <v>71346000</v>
       </c>
       <c r="BR3" t="n">
-        <v>85665000</v>
+        <v>71346000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>118726600</v>
@@ -2019,47 +2043,47 @@
         <v>118726600</v>
       </c>
       <c r="D4" t="n">
-        <v>422655000</v>
+        <v>175276000</v>
       </c>
       <c r="E4" t="n">
-        <v>495992000</v>
+        <v>264001000</v>
       </c>
       <c r="F4" t="n">
-        <v>1089342000</v>
+        <v>889204000</v>
       </c>
       <c r="G4" t="n">
-        <v>1583343000</v>
+        <v>1150145000</v>
       </c>
       <c r="H4" t="n">
-        <v>64397000</v>
+        <v>9163000</v>
       </c>
       <c r="I4" t="n">
-        <v>1089342000</v>
+        <v>889204000</v>
       </c>
       <c r="J4" t="n">
-        <v>1991000</v>
+        <v>3060000</v>
       </c>
       <c r="K4" t="n">
-        <v>1089342000</v>
+        <v>889204000</v>
       </c>
       <c r="L4" t="n">
-        <v>1403306000</v>
+        <v>1020968000</v>
       </c>
       <c r="M4" t="n">
-        <v>1088680000</v>
+        <v>888155000</v>
       </c>
       <c r="N4" t="n">
-        <v>-662000</v>
+        <v>-1049000</v>
       </c>
       <c r="O4" t="n">
-        <v>1089342000</v>
+        <v>889204000</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>108253000</v>
+        <v>99901000</v>
       </c>
       <c r="R4" t="n">
-        <v>-1489226000</v>
+        <v>-1657120000</v>
       </c>
       <c r="S4" t="n">
         <v>2440792000</v>
@@ -2071,205 +2095,199 @@
         <v>23745000</v>
       </c>
       <c r="V4" t="n">
-        <v>603784000</v>
+        <v>558705000</v>
       </c>
       <c r="W4" t="n">
-        <v>306610000</v>
+        <v>215780000</v>
       </c>
       <c r="X4" t="n">
-        <v>27491000</v>
+        <v>7334000</v>
       </c>
       <c r="Y4" t="n">
-        <v>34768000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>87138000</v>
+        <v>74884000</v>
       </c>
       <c r="AA4" t="n">
-        <v>314195000</v>
+        <v>133562000</v>
       </c>
       <c r="AB4" t="n">
-        <v>231000</v>
+        <v>1798000</v>
       </c>
       <c r="AC4" t="n">
-        <v>313964000</v>
+        <v>131764000</v>
       </c>
       <c r="AD4" t="n">
-        <v>297174000</v>
+        <v>342925000</v>
       </c>
       <c r="AE4" t="n">
-        <v>181797000</v>
+        <v>130439000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1760000</v>
+        <v>1262000</v>
       </c>
       <c r="AG4" t="n">
-        <v>180037000</v>
+        <v>129177000</v>
       </c>
       <c r="AH4" t="n">
-        <v>107222000</v>
+        <v>195486000</v>
       </c>
       <c r="AI4" t="n">
-        <v>52491000</v>
+        <v>140313000</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>54731000</v>
+        <v>55173000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1692464000</v>
+        <v>1446860000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1330893000</v>
-      </c>
-      <c r="AN4" t="n">
+        <v>1094772000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
         <v>0</v>
       </c>
-      <c r="AO4" t="n">
-        <v>12877000</v>
-      </c>
       <c r="AP4" t="n">
-        <v>12717000</v>
+        <v>4713000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9040000</v>
+        <v>1956000</v>
       </c>
       <c r="AR4" t="n">
-        <v>3677000</v>
+        <v>2757000</v>
       </c>
       <c r="AS4" t="n">
-        <v>767219000</v>
+        <v>669164000</v>
       </c>
       <c r="AT4" t="n">
-        <v>486820000</v>
+        <v>394772000</v>
       </c>
       <c r="AU4" t="n">
-        <v>486820000</v>
+        <v>394772000</v>
       </c>
       <c r="AV4" t="n">
-        <v>516185000</v>
+        <v>420895000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-931483000</v>
+        <v>-985221000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1447668000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
+        <v>1406116000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>21458000</v>
+        <v>17709000</v>
       </c>
       <c r="BA4" t="n">
-        <v>215107000</v>
+        <v>178204000</v>
       </c>
       <c r="BB4" t="n">
-        <v>58933000</v>
+        <v>55030000</v>
       </c>
       <c r="BC4" t="n">
-        <v>5910000</v>
+        <v>5168000</v>
       </c>
       <c r="BD4" t="n">
-        <v>1167718000</v>
+        <v>1167714000</v>
       </c>
       <c r="BE4" t="n">
-        <v>361571000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
+        <v>352088000</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>5651000</v>
+        <v>6932000</v>
       </c>
       <c r="BH4" t="n">
-        <v>33442000</v>
+        <v>23818000</v>
       </c>
       <c r="BI4" t="n">
-        <v>20646000</v>
+        <v>9709000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>111000</v>
+        <v>6306000</v>
       </c>
       <c r="BK4" t="n">
-        <v>12685000</v>
+        <v>7803000</v>
       </c>
       <c r="BL4" t="n">
-        <v>160050000</v>
+        <v>162488000</v>
       </c>
       <c r="BM4" t="n">
-        <v>10267000</v>
+        <v>9613000</v>
       </c>
       <c r="BN4" t="n">
-        <v>74017000</v>
+        <v>57642000</v>
       </c>
       <c r="BO4" t="n">
-        <v>78144000</v>
+        <v>91595000</v>
       </c>
       <c r="BP4" t="n">
-        <v>6798000</v>
+        <v>5930000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>71346000</v>
+        <v>85665000</v>
       </c>
       <c r="BR4" t="n">
-        <v>71346000</v>
+        <v>85665000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>118726600</v>
+        <v>118726617</v>
       </c>
       <c r="C5" t="n">
-        <v>118726600</v>
+        <v>118726617</v>
       </c>
       <c r="D5" t="n">
-        <v>202686000</v>
+        <v>159908000</v>
       </c>
       <c r="E5" t="n">
-        <v>272841000</v>
+        <v>264231000</v>
       </c>
       <c r="F5" t="n">
-        <v>1200263000</v>
+        <v>800489000</v>
       </c>
       <c r="G5" t="n">
-        <v>1469902000</v>
+        <v>1062923000</v>
       </c>
       <c r="H5" t="n">
-        <v>68327000</v>
+        <v>-46135000</v>
       </c>
       <c r="I5" t="n">
-        <v>1200263000</v>
+        <v>800489000</v>
       </c>
       <c r="J5" t="n">
-        <v>3202000</v>
+        <v>1797000</v>
       </c>
       <c r="K5" t="n">
-        <v>1200263000</v>
+        <v>800489000</v>
       </c>
       <c r="L5" t="n">
-        <v>1220706000</v>
+        <v>906319000</v>
       </c>
       <c r="M5" t="n">
-        <v>1198550000</v>
+        <v>798726000</v>
       </c>
       <c r="N5" t="n">
-        <v>-1713000</v>
+        <v>-1763000</v>
       </c>
       <c r="O5" t="n">
-        <v>1200263000</v>
+        <v>800489000</v>
       </c>
       <c r="P5" t="n">
-        <v>1518000</v>
+        <v>233000</v>
       </c>
       <c r="Q5" t="n">
-        <v>108253000</v>
+        <v>99901000</v>
       </c>
       <c r="R5" t="n">
-        <v>-1388526000</v>
+        <v>-1745636000</v>
       </c>
       <c r="S5" t="n">
         <v>2440792000</v>
@@ -2281,151 +2299,133 @@
         <v>23745000</v>
       </c>
       <c r="V5" t="n">
-        <v>565752000</v>
+        <v>568589000</v>
       </c>
       <c r="W5" t="n">
-        <v>159942000</v>
+        <v>163767000</v>
       </c>
       <c r="X5" t="n">
-        <v>22723000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>27270000</v>
-      </c>
+        <v>4288000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>88190000</v>
+        <v>52962000</v>
       </c>
       <c r="AA5" t="n">
-        <v>21759000</v>
+        <v>106517000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1316000</v>
+        <v>687000</v>
       </c>
       <c r="AC5" t="n">
-        <v>20443000</v>
+        <v>105830000</v>
       </c>
       <c r="AD5" t="n">
-        <v>405810000</v>
+        <v>404822000</v>
       </c>
       <c r="AE5" t="n">
-        <v>251082000</v>
+        <v>157714000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1886000</v>
+        <v>1110000</v>
       </c>
       <c r="AG5" t="n">
-        <v>249196000</v>
+        <v>156604000</v>
       </c>
       <c r="AH5" t="n">
-        <v>148902000</v>
+        <v>231933000</v>
       </c>
       <c r="AI5" t="n">
-        <v>64200000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
+        <v>113184000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>84702000</v>
+        <v>117763000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1764302000</v>
+        <v>1367315000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1290165000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1632000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
+        <v>1008628000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>35867000</v>
+        <v>3851000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24267000</v>
+        <v>3106000</v>
       </c>
       <c r="AR5" t="n">
-        <v>11600000</v>
+        <v>745000</v>
       </c>
       <c r="AS5" t="n">
-        <v>650996000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>557560000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>557560000</v>
-      </c>
+        <v>586369000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>593605000</v>
+        <v>418408000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-907807000</v>
+        <v>-986804000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1501412000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1632000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>24933000</v>
-      </c>
+        <v>1405212000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>263507000</v>
+        <v>179029000</v>
       </c>
       <c r="BB5" t="n">
-        <v>62278000</v>
+        <v>53581000</v>
       </c>
       <c r="BC5" t="n">
-        <v>6306000</v>
+        <v>4898000</v>
       </c>
       <c r="BD5" t="n">
-        <v>1167689000</v>
+        <v>1167704000</v>
       </c>
       <c r="BE5" t="n">
-        <v>474137000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>72150000</v>
-      </c>
+        <v>358687000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>3446000</v>
+        <v>7567000</v>
       </c>
       <c r="BH5" t="n">
-        <v>46593000</v>
+        <v>25342000</v>
       </c>
       <c r="BI5" t="n">
-        <v>28835000</v>
+        <v>9939000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1275000</v>
+        <v>6354000</v>
       </c>
       <c r="BK5" t="n">
-        <v>16483000</v>
+        <v>9049000</v>
       </c>
       <c r="BL5" t="n">
-        <v>187427000</v>
+        <v>125674000</v>
       </c>
       <c r="BM5" t="n">
-        <v>7865000</v>
+        <v>9665000</v>
       </c>
       <c r="BN5" t="n">
-        <v>84612000</v>
+        <v>84113000</v>
       </c>
       <c r="BO5" t="n">
-        <v>72044000</v>
+        <v>106326000</v>
       </c>
       <c r="BP5" t="n">
-        <v>5091000</v>
+        <v>3800000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>66953000</v>
+        <v>102526000</v>
       </c>
       <c r="BR5" t="n">
-        <v>66953000</v>
+        <v>102526000</v>
       </c>
     </row>
   </sheetData>
@@ -2676,66 +2676,72 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-15549000</v>
+        <v>-45113000</v>
       </c>
       <c r="C2" t="n">
-        <v>-215945000</v>
+        <v>-112412000</v>
       </c>
       <c r="D2" t="n">
-        <v>218922000</v>
+        <v>184825000</v>
       </c>
       <c r="E2" t="n">
-        <v>-8476000</v>
+        <v>-44535000</v>
       </c>
       <c r="F2" t="n">
-        <v>102526000</v>
+        <v>66953000</v>
       </c>
       <c r="G2" t="n">
-        <v>85665000</v>
+        <v>63634000</v>
       </c>
       <c r="H2" t="n">
-        <v>293000</v>
+        <v>5261000</v>
       </c>
       <c r="I2" t="n">
-        <v>16568000</v>
+        <v>-1942000</v>
       </c>
       <c r="J2" t="n">
-        <v>-14275000</v>
+        <v>54651000</v>
       </c>
       <c r="K2" t="n">
-        <v>-15989000</v>
+        <v>-15166000</v>
       </c>
       <c r="L2" t="n">
-        <v>2977000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>72413000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
       <c r="O2" t="n">
-        <v>2977000</v>
+        <v>72413000</v>
       </c>
       <c r="P2" t="n">
-        <v>-215945000</v>
+        <v>-112412000</v>
       </c>
       <c r="Q2" t="n">
-        <v>218922000</v>
+        <v>184825000</v>
       </c>
       <c r="R2" t="n">
-        <v>37916000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>-56015000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-68021000</v>
+      </c>
       <c r="T2" t="n">
-        <v>10909000</v>
+        <v>13408000</v>
       </c>
       <c r="U2" t="n">
-        <v>53000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>53000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
@@ -2743,408 +2749,404 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1621000</v>
+        <v>43125000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1621000</v>
+        <v>43125000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2622000</v>
+        <v>-3323000</v>
       </c>
       <c r="AC2" t="n">
-        <v>4345000</v>
+        <v>8000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1723000</v>
+        <v>-3331000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-6753000</v>
+        <v>-41204000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-7073000</v>
+        <v>-578000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3265000</v>
+        <v>-51000</v>
       </c>
       <c r="AH2" t="n">
-        <v>15667000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>8756000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6979000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>39989000</v>
+        <v>55497000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1175000</v>
+        <v>-22610000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-23147000</v>
+        <v>-31110000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1246000</v>
+        <v>2378000</v>
       </c>
       <c r="AN2" t="n">
-        <v>233000</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>2317000</v>
+        <v>11700000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5052000</v>
+        <v>11403000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5052000</v>
+        <v>11403000</v>
       </c>
       <c r="AR2" t="n">
-        <v>88763000</v>
+        <v>-88678000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-4213000</v>
+        <v>-3000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1235000</v>
+        <v>4656000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-110956000</v>
+        <v>188631000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>6838000</v>
+        <v>-133875000</v>
       </c>
       <c r="C3" t="n">
-        <v>-244225000</v>
+        <v>-199295000</v>
       </c>
       <c r="D3" t="n">
-        <v>240399000</v>
+        <v>275695000</v>
       </c>
       <c r="E3" t="n">
-        <v>-14713000</v>
+        <v>-134809000</v>
       </c>
       <c r="F3" t="n">
-        <v>85665000</v>
+        <v>71346000</v>
       </c>
       <c r="G3" t="n">
-        <v>71346000</v>
+        <v>66953000</v>
       </c>
       <c r="H3" t="n">
-        <v>-5868000</v>
+        <v>-1788000</v>
       </c>
       <c r="I3" t="n">
-        <v>20187000</v>
+        <v>6181000</v>
       </c>
       <c r="J3" t="n">
-        <v>-25660000</v>
+        <v>52177000</v>
       </c>
       <c r="K3" t="n">
-        <v>-19768000</v>
+        <v>-22230000</v>
       </c>
       <c r="L3" t="n">
-        <v>-3826000</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>76400000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-8000000</v>
+      </c>
       <c r="O3" t="n">
-        <v>-3826000</v>
+        <v>76400000</v>
       </c>
       <c r="P3" t="n">
-        <v>-244225000</v>
+        <v>-199295000</v>
       </c>
       <c r="Q3" t="n">
-        <v>240399000</v>
+        <v>275695000</v>
       </c>
       <c r="R3" t="n">
-        <v>24296000</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>-46930000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>72551000</v>
+      </c>
       <c r="T3" t="n">
-        <v>13985000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>335000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>335000</v>
-      </c>
+        <v>14238000</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>1924000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1924000</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>18951000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>18951000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2834000</v>
+        <v>-4177000</v>
       </c>
       <c r="AC3" t="n">
-        <v>72000</v>
+        <v>1090000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2906000</v>
+        <v>-5267000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-11807000</v>
+        <v>-129542000</v>
       </c>
       <c r="AF3" t="n">
-        <v>21551000</v>
+        <v>934000</v>
       </c>
       <c r="AG3" t="n">
+        <v>-247000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>6720000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-6786000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-23182000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>13042000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>23646000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>7032000</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>-2614000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7101000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>7101000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-529000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2218000</v>
+      </c>
+      <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>70312000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>335000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>61216000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>8908000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>188000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>5783000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>4609000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>6098000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6098000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3933000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-869000</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-4606000</v>
-      </c>
       <c r="AU3" t="n">
-        <v>-164198000</v>
+        <v>-112639000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-133875000</v>
+        <v>6838000</v>
       </c>
       <c r="C4" t="n">
-        <v>-199295000</v>
+        <v>-244225000</v>
       </c>
       <c r="D4" t="n">
-        <v>275695000</v>
+        <v>240399000</v>
       </c>
       <c r="E4" t="n">
-        <v>-134809000</v>
+        <v>-14713000</v>
       </c>
       <c r="F4" t="n">
+        <v>85665000</v>
+      </c>
+      <c r="G4" t="n">
         <v>71346000</v>
       </c>
-      <c r="G4" t="n">
-        <v>66953000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-1788000</v>
+        <v>-5868000</v>
       </c>
       <c r="I4" t="n">
-        <v>6181000</v>
+        <v>20187000</v>
       </c>
       <c r="J4" t="n">
-        <v>52177000</v>
+        <v>-25660000</v>
       </c>
       <c r="K4" t="n">
-        <v>-22230000</v>
+        <v>-19768000</v>
       </c>
       <c r="L4" t="n">
-        <v>76400000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-8000000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-8000000</v>
-      </c>
+        <v>-3826000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>76400000</v>
+        <v>-3826000</v>
       </c>
       <c r="P4" t="n">
-        <v>-199295000</v>
+        <v>-244225000</v>
       </c>
       <c r="Q4" t="n">
-        <v>275695000</v>
+        <v>240399000</v>
       </c>
       <c r="R4" t="n">
-        <v>-46930000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>72551000</v>
-      </c>
+        <v>24296000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>14238000</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+        <v>13985000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>335000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>335000</v>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
+        <v>1924000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1924000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>18951000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>18951000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-2834000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>72000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-2906000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-11807000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>21551000</v>
+      </c>
+      <c r="AG4" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AH4" t="n">
+        <v>70312000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>335000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>61216000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>8908000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>188000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5783000</v>
+      </c>
+      <c r="AN4" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-4177000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-5267000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-129542000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>934000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-247000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>6720000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-6786000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-23182000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>13042000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>23646000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>7032000</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-2614000</v>
+        <v>4609000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7101000</v>
+        <v>6098000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7101000</v>
+        <v>6098000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-529000</v>
+        <v>3933000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2218000</v>
+        <v>-869000</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>-4606000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-112639000</v>
+        <v>-164198000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-45113000</v>
+        <v>-15549000</v>
       </c>
       <c r="C5" t="n">
-        <v>-112412000</v>
+        <v>-215945000</v>
       </c>
       <c r="D5" t="n">
-        <v>184825000</v>
+        <v>218922000</v>
       </c>
       <c r="E5" t="n">
-        <v>-44535000</v>
+        <v>-8476000</v>
       </c>
       <c r="F5" t="n">
-        <v>66953000</v>
+        <v>102526000</v>
       </c>
       <c r="G5" t="n">
-        <v>63634000</v>
+        <v>85665000</v>
       </c>
       <c r="H5" t="n">
-        <v>5261000</v>
+        <v>293000</v>
       </c>
       <c r="I5" t="n">
-        <v>-1942000</v>
+        <v>16568000</v>
       </c>
       <c r="J5" t="n">
-        <v>54651000</v>
+        <v>-14275000</v>
       </c>
       <c r="K5" t="n">
-        <v>-15166000</v>
+        <v>-15989000</v>
       </c>
       <c r="L5" t="n">
-        <v>72413000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+        <v>2977000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>72413000</v>
+        <v>2977000</v>
       </c>
       <c r="P5" t="n">
-        <v>-112412000</v>
+        <v>-215945000</v>
       </c>
       <c r="Q5" t="n">
-        <v>184825000</v>
+        <v>218922000</v>
       </c>
       <c r="R5" t="n">
-        <v>-56015000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-68021000</v>
-      </c>
+        <v>37916000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>13408000</v>
+        <v>10909000</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
+        <v>53000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>53000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
         <v>0</v>
       </c>
@@ -3152,70 +3154,68 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>43125000</v>
+        <v>1621000</v>
       </c>
       <c r="AA5" t="n">
-        <v>43125000</v>
+        <v>1621000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3323000</v>
+        <v>2622000</v>
       </c>
       <c r="AC5" t="n">
-        <v>8000</v>
+        <v>4345000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3331000</v>
+        <v>-1723000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-41204000</v>
+        <v>-6753000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-578000</v>
+        <v>-7073000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-51000</v>
+        <v>-3265000</v>
       </c>
       <c r="AH5" t="n">
-        <v>8756000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6979000</v>
-      </c>
+        <v>15667000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>55497000</v>
+        <v>39989000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-22610000</v>
+        <v>-1175000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-31110000</v>
+        <v>-23147000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2378000</v>
+        <v>1246000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>233000</v>
       </c>
       <c r="AO5" t="n">
-        <v>11700000</v>
+        <v>2317000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11403000</v>
+        <v>5052000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11403000</v>
+        <v>5052000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-88678000</v>
+        <v>88763000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-3000</v>
+        <v>-4213000</v>
       </c>
       <c r="AT5" t="n">
-        <v>4656000</v>
+        <v>1235000</v>
       </c>
       <c r="AU5" t="n">
-        <v>188631000</v>
+        <v>-110956000</v>
       </c>
     </row>
   </sheetData>
@@ -3745,182 +3745,182 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EI1" t="inlineStr">
@@ -4028,55 +4028,55 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.229</v>
+        <v>0.195</v>
       </c>
       <c r="V2" t="n">
-        <v>0.208</v>
+        <v>0.195</v>
       </c>
       <c r="W2" t="n">
-        <v>0.208</v>
+        <v>0.195</v>
       </c>
       <c r="X2" t="n">
-        <v>0.211</v>
+        <v>0.195</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.229</v>
+        <v>0.195</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.208</v>
+        <v>0.195</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.208</v>
+        <v>0.195</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.211</v>
+        <v>0.195</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.067</v>
+        <v>-0.206</v>
       </c>
       <c r="AE2" t="n">
-        <v>160001</v>
+        <v>50100</v>
       </c>
       <c r="AF2" t="n">
-        <v>160001</v>
+        <v>50100</v>
       </c>
       <c r="AG2" t="n">
-        <v>1399225</v>
+        <v>1406711</v>
       </c>
       <c r="AH2" t="n">
-        <v>272779</v>
+        <v>204025</v>
       </c>
       <c r="AI2" t="n">
-        <v>272779</v>
+        <v>204025</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.212</v>
+        <v>0.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.223</v>
+        <v>0.191</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -4085,13 +4085,13 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>30202924</v>
+        <v>27211126</v>
       </c>
       <c r="AO2" t="n">
-        <v>32624855</v>
+        <v>27780990</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.203</v>
+        <v>0.174</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.9</v>
@@ -4100,16 +4100,16 @@
         <v>121922.67</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.203</v>
+        <v>0.174</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.05841032</v>
+        <v>0.052624393</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.42306</v>
+        <v>0.3403</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.54414</v>
+        <v>0.5221749999999999</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4126,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>94747920</v>
+        <v>91756120</v>
       </c>
       <c r="BB2" t="n">
         <v>-0.25373</v>
@@ -4150,7 +4150,7 @@
         <v>4.313</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.04915372</v>
+        <v>0.04428472</v>
       </c>
       <c r="BJ2" t="n">
         <v>1751241600</v>
@@ -4165,7 +4165,7 @@
         <v>-131201000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-1.2</v>
+        <v>-1.18</v>
       </c>
       <c r="BO2" t="n">
         <v>0.68</v>
@@ -4179,16 +4179,16 @@
         <v>1713139200</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.183</v>
+        <v>0.177</v>
       </c>
       <c r="BS2" t="n">
-        <v>-1.933</v>
+        <v>-1.872</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.37260276</v>
+        <v>-0.54117644</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.212</v>
+        <v>0.191</v>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
@@ -4295,137 +4295,137 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CY2" t="b">
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>SOLARTECH INT'L</t>
+        </is>
+      </c>
+      <c r="CZ2" t="b">
         <v>0</v>
       </c>
-      <c r="CZ2" t="n">
+      <c r="DA2" t="n">
         <v>1033522200000</v>
       </c>
-      <c r="DA2" t="n">
-        <v>-0.017000005</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>0.208 - 0.211</t>
-        </is>
+      <c r="DB2" t="n">
+        <v>-0.003999993</v>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
+          <t>0.195 - 0.195</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DD2" t="n">
-        <v>1399225</v>
-      </c>
       <c r="DE2" t="n">
-        <v>0.009000002999999999</v>
+        <v>1406711</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.044334993</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>0.203 - 0.9</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.68799996</v>
+        <v>0.017000005</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0.09770118</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0.174 - 0.9</t>
+        </is>
       </c>
       <c r="DI2" t="n">
-        <v>-0.7644444</v>
+        <v>-0.709</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-37.260277</v>
+        <v>-0.7877778</v>
       </c>
       <c r="DK2" t="n">
+        <v>-54.117645</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Solartech International Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-2.0512786</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1781752577</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>finmb_882117</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DV2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
         <v>1740663291</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="DZ2" t="n">
         <v>1740663291</v>
       </c>
-      <c r="DM2" t="b">
+      <c r="EA2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.21106</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.49888906</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.33213997</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.61039436</v>
-      </c>
-      <c r="DS2" t="n">
+      <c r="EB2" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.1493</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.4387305</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.33117503</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.63422227</v>
+      </c>
+      <c r="EG2" t="n">
         <v>15</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="EH2" t="n">
         <v>15</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-7.4235826</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>finmb_882117</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="ED2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>1780381640</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>SOLARTECH INT'L</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Solartech International Holdings Limited</t>
-        </is>
       </c>
       <c r="EI2" t="b">
         <v>0</v>
